--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-08-31).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-08-31).xlsx
@@ -935,10 +935,10 @@
     <t>214</t>
   </si>
   <si>
-    <t>21</t>
+    <t>20</t>
   </si>
   <si>
-    <t>R$ 3.297,85</t>
+    <t>R$ 3.298,55</t>
   </si>
   <si>
     <t>36.8</t>
@@ -947,7 +947,7 @@
     <t>23.3</t>
   </si>
   <si>
-    <t>4.86</t>
+    <t>4.87</t>
   </si>
   <si>
     <t>19.2</t>
@@ -959,7 +959,7 @@
     <t>6.5</t>
   </si>
   <si>
-    <t>44.0%</t>
+    <t>44.2%</t>
   </si>
   <si>
     <t>19.3%</t>
@@ -10181,7 +10181,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>51</v>
@@ -10211,18 +10211,30 @@
         <v>58</v>
       </c>
       <c r="L58" s="4"/>
-      <c r="M58" s="5"/>
-      <c r="N58" s="6"/>
+      <c r="M58" s="5">
+        <v>3433.1300000000001</v>
+      </c>
+      <c r="N58" s="6">
+        <v>39</v>
+      </c>
       <c r="O58" s="6">
         <v>31</v>
       </c>
-      <c r="P58" s="7"/>
-      <c r="Q58" s="8"/>
-      <c r="R58" s="8"/>
+      <c r="P58" s="7">
+        <v>5.0223684210526311</v>
+      </c>
+      <c r="Q58" s="8">
+        <v>17.240861290322577</v>
+      </c>
+      <c r="R58" s="8">
+        <v>5.3394433333333335</v>
+      </c>
       <c r="S58" s="8">
         <v>7</v>
       </c>
-      <c r="T58" s="9"/>
+      <c r="T58" s="9">
+        <v>0.29032258064516131</v>
+      </c>
       <c r="U58" s="9">
         <v>0.064516129032258063</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-08-31).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-08-31).xlsx
@@ -935,31 +935,31 @@
     <t>214</t>
   </si>
   <si>
-    <t>20</t>
+    <t>17</t>
   </si>
   <si>
-    <t>R$ 3.298,55</t>
+    <t>R$ 3.273,48</t>
   </si>
   <si>
-    <t>36.8</t>
+    <t>36.5</t>
   </si>
   <si>
     <t>23.3</t>
   </si>
   <si>
-    <t>4.87</t>
+    <t>4.86</t>
   </si>
   <si>
     <t>19.2</t>
   </si>
   <si>
-    <t>7.6</t>
+    <t>7.7</t>
   </si>
   <si>
     <t>6.5</t>
   </si>
   <si>
-    <t>44.2%</t>
+    <t>44.5%</t>
   </si>
   <si>
     <t>19.3%</t>
@@ -6855,7 +6855,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6885,14 +6885,26 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
+      <c r="M36" s="5">
+        <v>2960.46</v>
+      </c>
+      <c r="N36" s="6">
+        <v>41</v>
+      </c>
       <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
+      <c r="P36" s="7">
+        <v>3.5581292682926828</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>18.661310714285715</v>
+      </c>
+      <c r="R36" s="8">
+        <v>8.4198730769230767</v>
+      </c>
       <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
+      <c r="T36" s="9">
+        <v>0.42857142857142855</v>
+      </c>
       <c r="U36" s="9"/>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
@@ -9144,7 +9156,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9174,14 +9186,26 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>247.30000000000001</v>
+      </c>
+      <c r="N51" s="6">
+        <v>3</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+      <c r="P51" s="7">
+        <v>6.6833333333333336</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>25.449999999999999</v>
+      </c>
+      <c r="R51" s="8">
+        <v>14.0167</v>
+      </c>
       <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
+      <c r="T51" s="9">
+        <v>0</v>
+      </c>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
@@ -14846,7 +14870,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14874,14 +14898,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>1750.54</v>
+      </c>
+      <c r="N89" s="6">
+        <v>19</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>3.0379611111111111</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>21.2416625</v>
+      </c>
+      <c r="R89" s="8">
+        <v>14.958333333333334</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.375</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
